--- a/Excel/9. Conditional Formatting/Lecture_6_Formatting.xlsx
+++ b/Excel/9. Conditional Formatting/Lecture_6_Formatting.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DAA5F3-EBEB-4E9F-850A-38F09A660570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5F67D5-FDD9-48EA-86C4-55CAC21DFE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="862" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="26" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="31" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="32" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="31" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="EastAndWest">[1]INDEX!$D$91:$G$93,[1]INDEX!$D$96:$G$98</definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="22">
   <si>
     <t>Students</t>
   </si>
@@ -105,7 +106,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,8 +145,42 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +196,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -194,41 +241,181 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="18">
     <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FF4BD4DF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FF4BD4DF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FF4BD4DF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FF4BD4DF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FF4BD4DF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FF4BD4DF"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -237,6 +424,7 @@
   <colors>
     <mruColors>
       <color rgb="FF4BD4DF"/>
+      <color rgb="FFFFCCFF"/>
       <color rgb="FFFF5050"/>
     </mruColors>
   </colors>
@@ -1503,6 +1691,471 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A18B557-F76D-4356-B503-6CE4B1932B6C}">
+  <dimension ref="F6:N19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="6:14" ht="21" x14ac:dyDescent="0.3">
+      <c r="F6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="8">
+        <v>99</v>
+      </c>
+      <c r="H7" s="8">
+        <v>83</v>
+      </c>
+      <c r="I7" s="8">
+        <v>85</v>
+      </c>
+      <c r="J7" s="8">
+        <v>82</v>
+      </c>
+      <c r="K7" s="8">
+        <v>69</v>
+      </c>
+      <c r="L7" s="8">
+        <v>92</v>
+      </c>
+      <c r="M7" s="8">
+        <v>510</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="8" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="8">
+        <v>85</v>
+      </c>
+      <c r="H8" s="8">
+        <v>53</v>
+      </c>
+      <c r="I8" s="8">
+        <v>43</v>
+      </c>
+      <c r="J8" s="8">
+        <v>52</v>
+      </c>
+      <c r="K8" s="8">
+        <v>11</v>
+      </c>
+      <c r="L8" s="8">
+        <v>52</v>
+      </c>
+      <c r="M8" s="8">
+        <v>296</v>
+      </c>
+      <c r="N8" s="8">
+        <v>0.49333333333333335</v>
+      </c>
+    </row>
+    <row r="9" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="8">
+        <v>85</v>
+      </c>
+      <c r="H9" s="8">
+        <v>80</v>
+      </c>
+      <c r="I9" s="8">
+        <v>79</v>
+      </c>
+      <c r="J9" s="8">
+        <v>79</v>
+      </c>
+      <c r="K9" s="8">
+        <v>74</v>
+      </c>
+      <c r="L9" s="8">
+        <v>91</v>
+      </c>
+      <c r="M9" s="8">
+        <v>488</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0.81333333333333335</v>
+      </c>
+    </row>
+    <row r="10" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="8">
+        <v>100</v>
+      </c>
+      <c r="H10" s="8">
+        <v>99</v>
+      </c>
+      <c r="I10" s="8">
+        <v>82</v>
+      </c>
+      <c r="J10" s="8">
+        <v>98</v>
+      </c>
+      <c r="K10" s="8">
+        <v>81</v>
+      </c>
+      <c r="L10" s="8">
+        <v>62</v>
+      </c>
+      <c r="M10" s="8">
+        <v>522</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="11" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="8">
+        <v>45</v>
+      </c>
+      <c r="H11" s="8">
+        <v>60</v>
+      </c>
+      <c r="I11" s="8">
+        <v>30</v>
+      </c>
+      <c r="J11" s="8">
+        <v>59</v>
+      </c>
+      <c r="K11" s="8">
+        <v>45</v>
+      </c>
+      <c r="L11" s="8">
+        <v>60</v>
+      </c>
+      <c r="M11" s="8">
+        <v>299</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0.49833333333333335</v>
+      </c>
+    </row>
+    <row r="12" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="8">
+        <v>63</v>
+      </c>
+      <c r="H12" s="8">
+        <v>76</v>
+      </c>
+      <c r="I12" s="8">
+        <v>81</v>
+      </c>
+      <c r="J12" s="8">
+        <v>61</v>
+      </c>
+      <c r="K12" s="8">
+        <v>94</v>
+      </c>
+      <c r="L12" s="8">
+        <v>45</v>
+      </c>
+      <c r="M12" s="8">
+        <v>420</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="8">
+        <v>72</v>
+      </c>
+      <c r="H13" s="8">
+        <v>67</v>
+      </c>
+      <c r="I13" s="8">
+        <v>86</v>
+      </c>
+      <c r="J13" s="8">
+        <v>66</v>
+      </c>
+      <c r="K13" s="8">
+        <v>81</v>
+      </c>
+      <c r="L13" s="8">
+        <v>58</v>
+      </c>
+      <c r="M13" s="8">
+        <v>430</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0.71666666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="8">
+        <v>82</v>
+      </c>
+      <c r="H14" s="8">
+        <v>63</v>
+      </c>
+      <c r="I14" s="8">
+        <v>72</v>
+      </c>
+      <c r="J14" s="8">
+        <v>80</v>
+      </c>
+      <c r="K14" s="8">
+        <v>53</v>
+      </c>
+      <c r="L14" s="8">
+        <v>92</v>
+      </c>
+      <c r="M14" s="8">
+        <v>442</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0.73666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="8">
+        <v>68</v>
+      </c>
+      <c r="H15" s="8">
+        <v>93</v>
+      </c>
+      <c r="I15" s="8">
+        <v>71</v>
+      </c>
+      <c r="J15" s="8">
+        <v>92</v>
+      </c>
+      <c r="K15" s="8">
+        <v>96</v>
+      </c>
+      <c r="L15" s="8">
+        <v>65</v>
+      </c>
+      <c r="M15" s="8">
+        <v>485</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0.80833333333333335</v>
+      </c>
+    </row>
+    <row r="16" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="8">
+        <v>59</v>
+      </c>
+      <c r="H16" s="8">
+        <v>89</v>
+      </c>
+      <c r="I16" s="8">
+        <v>95</v>
+      </c>
+      <c r="J16" s="8">
+        <v>57</v>
+      </c>
+      <c r="K16" s="8">
+        <v>31</v>
+      </c>
+      <c r="L16" s="8">
+        <v>75</v>
+      </c>
+      <c r="M16" s="8">
+        <v>406</v>
+      </c>
+      <c r="N16" s="8">
+        <v>0.67666666666666664</v>
+      </c>
+    </row>
+    <row r="17" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="8">
+        <v>84</v>
+      </c>
+      <c r="H17" s="8">
+        <v>43</v>
+      </c>
+      <c r="I17" s="8">
+        <v>93</v>
+      </c>
+      <c r="J17" s="8">
+        <v>42</v>
+      </c>
+      <c r="K17" s="8">
+        <v>52</v>
+      </c>
+      <c r="L17" s="8">
+        <v>75</v>
+      </c>
+      <c r="M17" s="8">
+        <v>389</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0.64833333333333332</v>
+      </c>
+    </row>
+    <row r="18" spans="6:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="8">
+        <v>94</v>
+      </c>
+      <c r="H18" s="8">
+        <v>72</v>
+      </c>
+      <c r="I18" s="8">
+        <v>54</v>
+      </c>
+      <c r="J18" s="8">
+        <v>92</v>
+      </c>
+      <c r="K18" s="8">
+        <v>32</v>
+      </c>
+      <c r="L18" s="8">
+        <v>57</v>
+      </c>
+      <c r="M18" s="8">
+        <v>401</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0.66833333333333333</v>
+      </c>
+    </row>
+    <row r="19" spans="6:14" ht="21" x14ac:dyDescent="0.3">
+      <c r="F19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="10">
+        <v>78</v>
+      </c>
+      <c r="H19" s="10">
+        <v>73.166666666666671</v>
+      </c>
+      <c r="I19" s="10">
+        <v>72.583333333333329</v>
+      </c>
+      <c r="J19" s="10">
+        <v>71.666666666666671</v>
+      </c>
+      <c r="K19" s="10">
+        <v>59.916666666666664</v>
+      </c>
+      <c r="L19" s="10">
+        <v>68.666666666666671</v>
+      </c>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H7:H18">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M18">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="5Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="20"/>
+        <cfvo type="percent" val="40"/>
+        <cfvo type="percent" val="60"/>
+        <cfvo type="percent" val="80"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{87CC8669-AE73-4D8C-A870-F1F96C39CF5D}">
+            <x14:iconSet iconSet="3Stars">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>33</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>67</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>N7:N18</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7799719E-3EA7-44DE-8757-895687B22B48}">
   <dimension ref="D5:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
